--- a/data/trans_dic/P11_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,35; 36,32</t>
+          <t>30,74; 36,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,54; 37,88</t>
+          <t>31,54; 37,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,83; 37,37</t>
+          <t>30,73; 37,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 48,24</t>
+          <t>40,23; 48,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,32; 49,44</t>
+          <t>43,86; 49,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,26; 54,76</t>
+          <t>49,24; 55,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,85; 56,26</t>
+          <t>50,04; 56,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,57; 66,98</t>
+          <t>61,31; 67,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,06; 43,06</t>
+          <t>38,94; 43,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,84; 46,95</t>
+          <t>42,46; 46,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,41; 47,33</t>
+          <t>42,44; 47,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,88; 58,69</t>
+          <t>53,65; 58,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 13,15</t>
+          <t>10,04; 13,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,65</t>
+          <t>11,47; 14,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,83; 17,05</t>
+          <t>13,77; 17,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 25,68</t>
+          <t>15,75; 25,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 20,57</t>
+          <t>16,59; 20,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 22,71</t>
+          <t>18,71; 22,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 22,44</t>
+          <t>18,73; 22,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,82; 54,14</t>
+          <t>28,83; 53,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 16,0</t>
+          <t>13,54; 16,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 17,88</t>
+          <t>15,47; 17,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 19,2</t>
+          <t>16,78; 19,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,68; 39,45</t>
+          <t>25,13; 40,28</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,38</t>
+          <t>7,63; 13,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 14,26</t>
+          <t>7,99; 14,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,75</t>
+          <t>7,19; 12,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,0</t>
+          <t>15,86; 22,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 20,64</t>
+          <t>13,68; 20,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,41</t>
+          <t>8,44; 14,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,83; 19,26</t>
+          <t>12,6; 19,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,14; 28,81</t>
+          <t>23,06; 29,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 15,59</t>
+          <t>11,16; 15,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,4</t>
+          <t>8,8; 13,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 15,16</t>
+          <t>10,79; 15,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,44; 24,73</t>
+          <t>20,19; 24,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,88; 19,62</t>
+          <t>16,92; 19,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 20,11</t>
+          <t>17,45; 20,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 20,02</t>
+          <t>17,29; 20,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 27,57</t>
+          <t>19,55; 27,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,56; 30,67</t>
+          <t>27,64; 30,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 32,92</t>
+          <t>29,64; 32,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,39; 30,49</t>
+          <t>27,32; 30,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,91; 52,38</t>
+          <t>35,85; 51,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,87</t>
+          <t>22,7; 24,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,08; 26,26</t>
+          <t>24,22; 26,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,86; 24,9</t>
+          <t>22,93; 24,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,37; 38,87</t>
+          <t>29,56; 40,44</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>313143; 374740</t>
+          <t>317123; 376700</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>306127; 367644</t>
+          <t>306073; 368717</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>231382; 280446</t>
+          <t>230568; 282786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206935; 248397</t>
+          <t>207172; 250666</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>582919; 650230</t>
+          <t>576774; 651438</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>658530; 732015</t>
+          <t>658205; 737358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>489959; 552914</t>
+          <t>491775; 556801</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>463800; 504590</t>
+          <t>461875; 506404</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>916728; 1010501</t>
+          <t>913881; 1010646</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>988573; 1083215</t>
+          <t>979789; 1081268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>735057; 820348</t>
+          <t>735603; 819183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>683306; 744345</t>
+          <t>680426; 740654</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>166573; 222703</t>
+          <t>170078; 220511</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>221262; 286132</t>
+          <t>224103; 285262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>285121; 351411</t>
+          <t>283732; 351987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>368304; 587772</t>
+          <t>360362; 589434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>260896; 326576</t>
+          <t>263361; 323615</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>330519; 398504</t>
+          <t>328332; 399302</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>364197; 444095</t>
+          <t>370830; 444658</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>644914; 1211366</t>
+          <t>645026; 1195170</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>445760; 525093</t>
+          <t>444188; 526152</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>568592; 662993</t>
+          <t>573574; 666500</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>677152; 775971</t>
+          <t>677963; 780289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1116824; 1785608</t>
+          <t>1137344; 1823327</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43027; 73773</t>
+          <t>42080; 71801</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37003; 68307</t>
+          <t>38254; 68370</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38865; 69024</t>
+          <t>38940; 68507</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103192; 141946</t>
+          <t>102316; 143364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64508; 98348</t>
+          <t>65154; 98085</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38029; 66081</t>
+          <t>38718; 66521</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70228; 105434</t>
+          <t>68951; 105350</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>152550; 189930</t>
+          <t>151999; 192944</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>114570; 160279</t>
+          <t>114685; 161209</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83648; 125659</t>
+          <t>82553; 127079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116467; 164983</t>
+          <t>117402; 164385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>266668; 322548</t>
+          <t>263331; 318915</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>552983; 642865</t>
+          <t>554337; 643076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>593785; 684369</t>
+          <t>593790; 689994</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>575905; 671295</t>
+          <t>579602; 671264</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>673187; 950897</t>
+          <t>674185; 941163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>931344; 1036340</t>
+          <t>933971; 1042379</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1053890; 1168678</t>
+          <t>1052307; 1169965</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>961333; 1070121</t>
+          <t>958740; 1066126</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1310531; 1911746</t>
+          <t>1308561; 1863316</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1514374; 1655188</t>
+          <t>1510899; 1649700</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1674321; 1825749</t>
+          <t>1684192; 1826680</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1568432; 1708508</t>
+          <t>1573886; 1713275</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2084771; 2759438</t>
+          <t>2098662; 2870540</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P11_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,74; 36,51</t>
+          <t>30,58; 36,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,54; 37,99</t>
+          <t>31,31; 37,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,73; 37,68</t>
+          <t>30,47; 37,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,23; 48,68</t>
+          <t>39,21; 46,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,86; 49,53</t>
+          <t>44,09; 49,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,24; 55,16</t>
+          <t>49,34; 54,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,04; 56,65</t>
+          <t>49,86; 56,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,31; 67,22</t>
+          <t>60,69; 66,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,94; 43,06</t>
+          <t>38,93; 42,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,46; 46,86</t>
+          <t>42,6; 46,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,44; 47,26</t>
+          <t>42,4; 47,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,65; 58,4</t>
+          <t>52,51; 57,02</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,04; 13,02</t>
+          <t>9,95; 12,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 14,61</t>
+          <t>11,35; 14,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 17,08</t>
+          <t>13,75; 17,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,75; 25,75</t>
+          <t>22,81; 26,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,59; 20,38</t>
+          <t>16,34; 20,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,71; 22,75</t>
+          <t>18,84; 22,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,73; 22,46</t>
+          <t>18,76; 22,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,83; 53,42</t>
+          <t>29,16; 32,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 16,04</t>
+          <t>13,61; 16,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 17,97</t>
+          <t>15,41; 17,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 19,31</t>
+          <t>16,61; 19,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,13; 40,28</t>
+          <t>26,51; 29,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,02</t>
+          <t>7,85; 13,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 14,27</t>
+          <t>7,88; 14,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,66</t>
+          <t>7,22; 12,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 22,22</t>
+          <t>15,74; 21,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 20,59</t>
+          <t>13,43; 20,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,5</t>
+          <t>8,39; 14,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,6; 19,25</t>
+          <t>12,82; 19,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,06; 29,27</t>
+          <t>23,37; 29,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,68</t>
+          <t>11,34; 15,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,55</t>
+          <t>8,51; 12,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 15,1</t>
+          <t>10,81; 15,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,19; 24,45</t>
+          <t>20,7; 24,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 19,63</t>
+          <t>16,88; 19,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 20,28</t>
+          <t>17,51; 20,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 20,02</t>
+          <t>17,2; 20,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 27,29</t>
+          <t>24,97; 28,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,64; 30,85</t>
+          <t>27,78; 30,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 32,95</t>
+          <t>29,54; 32,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,32; 30,38</t>
+          <t>27,32; 30,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,85; 51,05</t>
+          <t>35,79; 38,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,79</t>
+          <t>22,66; 24,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,22; 26,27</t>
+          <t>24,16; 26,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,93; 24,97</t>
+          <t>22,7; 24,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 40,44</t>
+          <t>30,93; 33,01</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227190</t>
+          <t>247972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>483841</t>
+          <t>519275</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>711032</t>
+          <t>767248</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>317123; 376700</t>
+          <t>315469; 376737</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>306073; 368717</t>
+          <t>303877; 365182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230568; 282786</t>
+          <t>228619; 278909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207172; 250666</t>
+          <t>226865; 270314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>576774; 651438</t>
+          <t>579791; 651888</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>658205; 737358</t>
+          <t>659633; 733827</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>491775; 556801</t>
+          <t>490056; 555086</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>461875; 506404</t>
+          <t>497474; 542706</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>913881; 1010646</t>
+          <t>913538; 1008966</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>979789; 1081268</t>
+          <t>982856; 1079660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>735603; 819183</t>
+          <t>734906; 822231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>680426; 740654</t>
+          <t>734110; 797208</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510446</t>
+          <t>551915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>813076</t>
+          <t>669612</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1323521</t>
+          <t>1221527</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>170078; 220511</t>
+          <t>168478; 219758</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>224103; 285262</t>
+          <t>221750; 284820</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283732; 351987</t>
+          <t>283511; 354071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>360362; 589434</t>
+          <t>508361; 596694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>263361; 323615</t>
+          <t>259459; 323156</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>328332; 399302</t>
+          <t>330691; 399499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>370830; 444658</t>
+          <t>371270; 445230</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>645026; 1195170</t>
+          <t>633056; 709721</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>444188; 526152</t>
+          <t>446427; 531210</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>573574; 666500</t>
+          <t>571528; 664068</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>677963; 780289</t>
+          <t>671111; 774764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1137344; 1823327</t>
+          <t>1166477; 1290232</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>132837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>170402</t>
+          <t>192224</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>291994</t>
+          <t>325061</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42080; 71801</t>
+          <t>43270; 73137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38254; 68370</t>
+          <t>37728; 67848</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38940; 68507</t>
+          <t>39078; 69387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102316; 143364</t>
+          <t>111733; 154687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>65154; 98085</t>
+          <t>63959; 97846</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38718; 66521</t>
+          <t>38469; 68160</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68951; 105350</t>
+          <t>70186; 105920</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151999; 192944</t>
+          <t>171403; 213479</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>114685; 161209</t>
+          <t>116546; 163273</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82553; 127079</t>
+          <t>79777; 120805</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117402; 164385</t>
+          <t>117712; 167269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>263331; 318915</t>
+          <t>298768; 356999</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>859229</t>
+          <t>932725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1467319</t>
+          <t>1381111</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2326548</t>
+          <t>2313836</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>554337; 643076</t>
+          <t>553244; 639974</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>593790; 689994</t>
+          <t>595864; 697148</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>579602; 671264</t>
+          <t>576838; 671786</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>674185; 941163</t>
+          <t>878168; 989048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>933971; 1042379</t>
+          <t>938814; 1044684</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1052307; 1169965</t>
+          <t>1048894; 1166102</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>958740; 1066126</t>
+          <t>958661; 1071440</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1308561; 1863316</t>
+          <t>1332680; 1434760</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1510899; 1649700</t>
+          <t>1508456; 1648796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1684192; 1826680</t>
+          <t>1680038; 1822091</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1573886; 1713275</t>
+          <t>1557734; 1708725</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2098662; 2870540</t>
+          <t>2239439; 2390504</t>
         </is>
       </c>
     </row>
